--- a/S15/_S15_members.xlsx
+++ b/S15/_S15_members.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="161">
   <si>
     <t xml:space="preserve">Role</t>
   </si>
@@ -488,6 +488,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kw2</t>
   </si>
   <si>
     <t xml:space="preserve">admin1</t>
@@ -2002,30 +2005,28 @@
       <c r="D74" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="E74" s="3"/>
       <c r="F74" s="4" t="s">
-        <v>9</v>
+        <v>156</v>
       </c>
       <c r="G74" s="1" t="n">
         <f aca="true">RAND()</f>
-        <v>0.740398563174401</v>
+        <v>0.0640039485019511</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B75" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2036,13 +2037,12 @@
         <v>3</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="kokwei.fong@gmail.com"/>
-    <hyperlink ref="F74" r:id="rId2" display="kokwei.fong@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
